--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Barcode_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Barcode_report.xlsx
@@ -171,7 +171,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{d866279d-8341-4717-9d59-d6c775907e4d}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75745040-476f-472c-a9f0-37d3ab554109}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Barcode_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Barcode_report.xlsx
@@ -171,7 +171,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75745040-476f-472c-a9f0-37d3ab554109}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30c0fa02-c2db-4fe3-8f02-1e21bd55be9e}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Barcode_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Barcode_report.xlsx
@@ -171,7 +171,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30c0fa02-c2db-4fe3-8f02-1e21bd55be9e}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{d200aaad-f85b-40ea-9866-9b995fb54305}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
